--- a/config/unknowable-domain-generated/templates/UnknowableDomainReview.xlsx
+++ b/config/unknowable-domain-generated/templates/UnknowableDomainReview.xlsx
@@ -295,7 +295,7 @@
     <t>blocking_gap_ids</t>
   </si>
   <si>
-    <t>parser=split;separator=|;length=1..128</t>
+    <t>parser=split;separator=|;length=1..1024</t>
   </si>
   <si>
     <t>UnknowableDomainResearchGap</t>
